--- a/EKG_Kalite_Yönetim_Sistemi/10_Değişiklik ve Geçici Proses Kontrolü/01_MC1 - Talep, Etki ve Müşteri Onayı/EKG-PRJ-FRM-33_ptr_deneme_uretimi_ve_gecici_talimat_formu.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/10_Değişiklik ve Geçici Proses Kontrolü/01_MC1 - Talep, Etki ve Müşteri Onayı/EKG-PRJ-FRM-33_ptr_deneme_uretimi_ve_gecici_talimat_formu.xlsx
@@ -848,7 +848,8 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-PRJ-FRM-33&amp;C&amp;"Arial,Regular"&amp;11PTR Deneme Üretimi ve Geçici Talimat Formu</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 11.06.2026 | Revizyon: 23.09.2026
+Revizyon nedeni: Deneme ürün hesabı, sonuç kanıtı ve karar eklendi; geçici talimatın sınırı ve kontrollü dönüşü tanımlandı.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -894,7 +895,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04.05.2026</t>
+          <t xml:space="preserve">11.06.2026</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -1041,7 +1042,8 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-PRJ-FRM-33&amp;C&amp;"Arial,Regular"&amp;11PTR Deneme Üretimi ve Geçici Talimat Formu</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 11.06.2026 | Revizyon: 23.09.2026
+Revizyon nedeni: Deneme ürün hesabı, sonuç kanıtı ve karar eklendi; geçici talimatın sınırı ve kontrollü dönüşü tanımlandı.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>